--- a/artfynd/A 12854-2026 artfynd.xlsx
+++ b/artfynd/A 12854-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2707203</v>
+        <v>391123</v>
       </c>
       <c r="B2" t="n">
-        <v>95709</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220250</v>
+        <v>1263</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Ävjepilört</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Persicaria foliosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(H. Lindb.) Kitag.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Genbäcken, 200 m SSV, Vrm</t>
+          <t>Genbäcken, ävjepilört, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>419189.8579614095</v>
+        <v>419245</v>
       </c>
       <c r="R2" t="n">
-        <v>6613409.206694995</v>
+        <v>6613328</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,27 +735,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Nedre Ullerud</t>
+          <t>Övre Ullerud</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>S-For-0006</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2009-05-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2000-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2009-05-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2000-12-31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,21 +764,234 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Bäckravin</t>
+          <t>betad strandäng</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Värmland Floraväktarna</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Birgitta Mangsbo</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2707203</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98186</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Genbäcken, 200 m SSV, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>419190</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6613409</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Forshaga</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nedre Ullerud</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2009-05-09</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2009-05-09</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Bäckravin</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Crister Albinsson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Crister Albinsson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3332352</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106061</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221101</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Springkorn</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Impatiens noli-tangere</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Genbäcken, strax SV därom, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>419209</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6613499</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Forshaga</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Övre Ullerud</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2008-06-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2008-06-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>bäckravin</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Crister Albinsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Crister Albinsson, Stina Eriksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12854-2026 artfynd.xlsx
+++ b/artfynd/A 12854-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/391123</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2707203</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,8 +1007,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3332352</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>